--- a/salidas/empresas/CVX.xlsx
+++ b/salidas/empresas/CVX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.80403518676758</v>
+        <v>26.80402946472168</v>
       </c>
       <c r="C2" t="n">
         <v>59.38000106811523</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.6992301940918</v>
+        <v>25.6992244720459</v>
       </c>
       <c r="C3" t="n">
         <v>56.47999954223633</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.3771915435791</v>
+        <v>26.37719535827637</v>
       </c>
       <c r="C4" t="n">
         <v>57.97000122070312</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.76500701904297</v>
+        <v>27.76499176025391</v>
       </c>
       <c r="C5" t="n">
         <v>61.02000045776367</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.43916130065918</v>
+        <v>27.43915176391602</v>
       </c>
       <c r="C6" t="n">
         <v>59.79000091552734</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.48091316223145</v>
+        <v>28.48091125488281</v>
       </c>
       <c r="C7" t="n">
         <v>62.06000137329102</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>30.18812370300293</v>
+        <v>30.18811416625977</v>
       </c>
       <c r="C8" t="n">
         <v>65.77999877929688</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.78646469116211</v>
+        <v>29.78647041320801</v>
       </c>
       <c r="C9" t="n">
         <v>64.40000152587891</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.99922752380371</v>
+        <v>29.99923133850098</v>
       </c>
       <c r="C10" t="n">
         <v>64.86000061035156</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.08152198791504</v>
+        <v>31.0815315246582</v>
       </c>
       <c r="C11" t="n">
         <v>67.19999694824219</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>33.69861602783203</v>
+        <v>33.69862747192383</v>
       </c>
       <c r="C12" t="n">
         <v>72.31999969482422</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>34.26242446899414</v>
+        <v>34.262451171875</v>
       </c>
       <c r="C13" t="n">
         <v>73.52999877929688</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>33.9595832824707</v>
+        <v>33.95957565307617</v>
       </c>
       <c r="C14" t="n">
         <v>72.87999725341797</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.15755081176758</v>
+        <v>32.15755844116211</v>
       </c>
       <c r="C15" t="n">
         <v>68.51999664306641</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.50812149047852</v>
+        <v>36.50812911987305</v>
       </c>
       <c r="C17" t="n">
         <v>77.79000091552734</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.5213508605957</v>
+        <v>38.52134323120117</v>
       </c>
       <c r="C18" t="n">
         <v>81.48999786376953</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>39.82130432128906</v>
+        <v>39.82129669189453</v>
       </c>
       <c r="C19" t="n">
         <v>84.23999786376953</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>40.3034782409668</v>
+        <v>40.30348587036133</v>
       </c>
       <c r="C20" t="n">
         <v>85.26000213623047</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>41.77917098999023</v>
+        <v>41.77913665771484</v>
       </c>
       <c r="C21" t="n">
         <v>87.76000213623047</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>44.54983139038086</v>
+        <v>44.54983520507812</v>
       </c>
       <c r="C22" t="n">
         <v>93.58000183105469</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>43.56438064575195</v>
+        <v>43.56438827514648</v>
       </c>
       <c r="C23" t="n">
         <v>91.51000213623047</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>42.06489944458008</v>
+        <v>42.06490325927734</v>
       </c>
       <c r="C24" t="n">
         <v>87.76999664306641</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>44.72959899902344</v>
+        <v>44.72962188720703</v>
       </c>
       <c r="C25" t="n">
         <v>93.33000183105469</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.89862823486328</v>
+        <v>39.89863586425781</v>
       </c>
       <c r="C26" t="n">
         <v>83.25</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>41.83203125</v>
+        <v>41.83202362060547</v>
       </c>
       <c r="C27" t="n">
         <v>86.66000366210938</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.2044792175293</v>
+        <v>41.20448303222656</v>
       </c>
       <c r="C28" t="n">
         <v>85.36000061035156</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>46.41297149658203</v>
+        <v>46.41296005249023</v>
       </c>
       <c r="C29" t="n">
         <v>96.15000152587891</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>48.18161010742188</v>
+        <v>48.18159484863281</v>
       </c>
       <c r="C30" t="n">
         <v>99.15000152587891</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.17188262939453</v>
+        <v>48.171875</v>
       </c>
       <c r="C31" t="n">
         <v>99.12999725341797</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.09163284301758</v>
+        <v>41.09164047241211</v>
       </c>
       <c r="C32" t="n">
         <v>84.55999755859375</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>42.26420211791992</v>
+        <v>42.26419448852539</v>
       </c>
       <c r="C33" t="n">
         <v>86.31999969482422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.38404846191406</v>
+        <v>40.38405609130859</v>
       </c>
       <c r="C34" t="n">
         <v>82.48000335693359</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>36.52583312988281</v>
+        <v>36.52582931518555</v>
       </c>
       <c r="C35" t="n">
         <v>74.59999847412109</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>39.02007675170898</v>
+        <v>39.02006149291992</v>
       </c>
       <c r="C36" t="n">
         <v>79.01000213623047</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.53100967407227</v>
+        <v>36.53098678588867</v>
       </c>
       <c r="C37" t="n">
         <v>73.97000122070312</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>34.82717514038086</v>
+        <v>34.82716751098633</v>
       </c>
       <c r="C38" t="n">
         <v>70.51999664306641</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>30.25838661193848</v>
+        <v>30.25838279724121</v>
       </c>
       <c r="C39" t="n">
         <v>60.70999908447266</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.51299667358398</v>
+        <v>33.51299285888672</v>
       </c>
       <c r="C40" t="n">
         <v>67.23999786376953</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.9448127746582</v>
+        <v>32.94480895996094</v>
       </c>
       <c r="C41" t="n">
         <v>66.09999847412109</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>33.5503044128418</v>
+        <v>33.55031585693359</v>
       </c>
       <c r="C42" t="n">
         <v>66.66999816894531</v>
@@ -1267,11 +1279,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>33.33895111083984</v>
+        <v>33.33896636962891</v>
       </c>
       <c r="C43" t="n">
         <v>66.25</v>
@@ -1292,11 +1304,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.95935821533203</v>
+        <v>34.9593620300293</v>
       </c>
       <c r="C44" t="n">
         <v>69.47000122070312</v>
@@ -1317,11 +1329,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>35.54809188842773</v>
+        <v>35.548095703125</v>
       </c>
       <c r="C45" t="n">
         <v>69.94000244140625</v>
@@ -1342,7 +1354,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1367,11 +1379,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.90264129638672</v>
+        <v>38.90264511108398</v>
       </c>
       <c r="C47" t="n">
         <v>76.54000091552734</v>
@@ -1392,11 +1404,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.01414108276367</v>
+        <v>40.01415252685547</v>
       </c>
       <c r="C48" t="n">
         <v>78.04000091552734</v>
@@ -1417,11 +1429,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>39.47577285766602</v>
+        <v>39.47576904296875</v>
       </c>
       <c r="C49" t="n">
         <v>76.98999786376953</v>
@@ -1442,11 +1454,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>36.97874450683594</v>
+        <v>36.97872161865234</v>
       </c>
       <c r="C50" t="n">
         <v>72.12000274658203</v>
@@ -1467,11 +1479,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.42583847045898</v>
+        <v>37.42581558227539</v>
       </c>
       <c r="C51" t="n">
         <v>72.30000305175781</v>
@@ -1496,11 +1508,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.25313568115234</v>
+        <v>39.25313186645508</v>
       </c>
       <c r="C52" t="n">
         <v>75.83000183105469</v>
@@ -1525,11 +1537,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>42.15712356567383</v>
+        <v>42.15711975097656</v>
       </c>
       <c r="C53" t="n">
         <v>81.44000244140625</v>
@@ -1554,7 +1566,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1583,11 +1595,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.45547485351562</v>
+        <v>35.45546722412109</v>
       </c>
       <c r="C55" t="n">
         <v>67.86000061035156</v>
@@ -1612,11 +1624,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.81817626953125</v>
+        <v>39.81818389892578</v>
       </c>
       <c r="C56" t="n">
         <v>76.20999908447266</v>
@@ -1641,11 +1653,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>39.06726837158203</v>
+        <v>39.0672721862793</v>
       </c>
       <c r="C57" t="n">
         <v>74.08000183105469</v>
@@ -1670,11 +1682,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>42.74299621582031</v>
+        <v>42.74302291870117</v>
       </c>
       <c r="C58" t="n">
         <v>81.05000305175781</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>43.56040191650391</v>
+        <v>43.56043243408203</v>
       </c>
       <c r="C59" t="n">
         <v>82.59999847412109</v>
@@ -1728,11 +1740,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>43.06623077392578</v>
+        <v>43.06623458862305</v>
       </c>
       <c r="C60" t="n">
         <v>80.97000122070312</v>
@@ -1757,11 +1769,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>48.533935546875</v>
+        <v>48.53391265869141</v>
       </c>
       <c r="C61" t="n">
         <v>91.25</v>
@@ -1786,11 +1798,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>50.49123764038086</v>
+        <v>50.49124908447266</v>
       </c>
       <c r="C62" t="n">
         <v>94.93000030517578</v>
@@ -1815,11 +1827,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>55.59743499755859</v>
+        <v>55.59743881225586</v>
       </c>
       <c r="C63" t="n">
         <v>103.75</v>
@@ -1844,11 +1856,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>57.60163116455078</v>
+        <v>57.60163879394531</v>
       </c>
       <c r="C64" t="n">
         <v>107.4899978637695</v>
@@ -1873,11 +1885,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>58.64660263061523</v>
+        <v>58.64659881591797</v>
       </c>
       <c r="C65" t="n">
         <v>109.4400024414062</v>
@@ -1902,11 +1914,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>56.65380096435547</v>
+        <v>56.65378189086914</v>
       </c>
       <c r="C66" t="n">
         <v>104.9100036621094</v>
@@ -1931,11 +1943,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>55.53593063354492</v>
+        <v>55.53594970703125</v>
       </c>
       <c r="C67" t="n">
         <v>102.8399963378906</v>
@@ -1960,11 +1972,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.17314910888672</v>
+        <v>56.17317962646484</v>
       </c>
       <c r="C68" t="n">
         <v>104.0199966430664</v>
@@ -1989,11 +2001,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.803466796875</v>
+        <v>53.8034782409668</v>
       </c>
       <c r="C69" t="n">
         <v>98.83999633789062</v>
@@ -2018,11 +2030,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>50.40128707885742</v>
+        <v>50.40127182006836</v>
       </c>
       <c r="C70" t="n">
         <v>92.58999633789062</v>
@@ -2047,11 +2059,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>57.18389511108398</v>
+        <v>57.18386840820312</v>
       </c>
       <c r="C71" t="n">
         <v>105.0500030517578</v>
@@ -2076,11 +2088,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>56.41245269775391</v>
+        <v>56.41243743896484</v>
       </c>
       <c r="C72" t="n">
         <v>102.8199996948242</v>
@@ -2105,11 +2117,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>58.37661361694336</v>
+        <v>58.37663269042969</v>
       </c>
       <c r="C73" t="n">
         <v>106.4000015258789</v>
@@ -2134,11 +2146,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>56.57706832885742</v>
+        <v>56.57705307006836</v>
       </c>
       <c r="C74" t="n">
         <v>103.120002746582</v>
@@ -2163,7 +2175,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2192,11 +2204,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.27189254760742</v>
+        <v>59.27187347412109</v>
       </c>
       <c r="C76" t="n">
         <v>107.2099990844727</v>
@@ -2221,11 +2233,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>58.91250991821289</v>
+        <v>58.91250610351562</v>
       </c>
       <c r="C77" t="n">
         <v>106.5599975585938</v>
@@ -2250,7 +2262,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2279,11 +2291,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>58.85144805908203</v>
+        <v>58.85143280029297</v>
       </c>
       <c r="C79" t="n">
         <v>105.5</v>
@@ -2308,11 +2320,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>61.12740707397461</v>
+        <v>61.12743377685547</v>
       </c>
       <c r="C80" t="n">
         <v>109.5800018310547</v>
@@ -2337,11 +2349,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>63.0674934387207</v>
+        <v>63.06747436523438</v>
       </c>
       <c r="C81" t="n">
         <v>112.1600036621094</v>
@@ -2366,11 +2378,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>65.54161071777344</v>
+        <v>65.54158020019531</v>
       </c>
       <c r="C82" t="n">
         <v>116.5599975585938</v>
@@ -2395,11 +2407,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>61.98787307739258</v>
+        <v>61.98786926269531</v>
       </c>
       <c r="C83" t="n">
         <v>110.2399978637695</v>
@@ -2424,11 +2436,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>59.94182586669922</v>
+        <v>59.94186019897461</v>
       </c>
       <c r="C84" t="n">
         <v>105.6900024414062</v>
@@ -2453,11 +2465,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.33134460449219</v>
+        <v>61.33133316040039</v>
       </c>
       <c r="C85" t="n">
         <v>108.1399993896484</v>
@@ -2482,11 +2494,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>65.30703735351562</v>
+        <v>65.30706024169922</v>
       </c>
       <c r="C86" t="n">
         <v>115.1500015258789</v>
@@ -2511,11 +2523,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>66.95861053466797</v>
+        <v>66.95862579345703</v>
       </c>
       <c r="C87" t="n">
         <v>117.1500015258789</v>
@@ -2540,11 +2552,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>67.91313171386719</v>
+        <v>67.91313934326172</v>
       </c>
       <c r="C88" t="n">
         <v>118.8199996948242</v>
@@ -2569,11 +2581,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.73640441894531</v>
+        <v>69.73641967773438</v>
       </c>
       <c r="C89" t="n">
         <v>122.0100021362305</v>
@@ -2598,11 +2610,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>70.72518920898438</v>
+        <v>70.72517395019531</v>
       </c>
       <c r="C90" t="n">
         <v>122.75</v>
@@ -2627,11 +2639,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>68.18424987792969</v>
+        <v>68.18426513671875</v>
       </c>
       <c r="C91" t="n">
         <v>118.3399963378906</v>
@@ -2656,7 +2668,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2685,11 +2697,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>69.96166229248047</v>
+        <v>69.961669921875</v>
       </c>
       <c r="C93" t="n">
         <v>120.4300003051758</v>
@@ -2714,11 +2726,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>70.58327484130859</v>
+        <v>70.58328247070312</v>
       </c>
       <c r="C94" t="n">
         <v>121.5</v>
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>69.68864440917969</v>
+        <v>69.68865203857422</v>
       </c>
       <c r="C95" t="n">
         <v>119.9599990844727</v>
@@ -2772,7 +2784,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2801,11 +2813,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>73.173583984375</v>
+        <v>73.17356109619141</v>
       </c>
       <c r="C97" t="n">
         <v>124.9100036621094</v>
@@ -2830,7 +2842,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2859,11 +2871,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.16162872314453</v>
+        <v>68.16160583496094</v>
       </c>
       <c r="C99" t="n">
         <v>115.3300018310547</v>
@@ -2888,11 +2900,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>70.27745056152344</v>
+        <v>70.27743530273438</v>
       </c>
       <c r="C100" t="n">
         <v>118.9100036621094</v>
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2946,11 +2958,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.19007873535156</v>
+        <v>73.1900634765625</v>
       </c>
       <c r="C102" t="n">
         <v>122.7900009155273</v>
@@ -2975,11 +2987,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>77.81547546386719</v>
+        <v>77.81549072265625</v>
       </c>
       <c r="C103" t="n">
         <v>130.5500030517578</v>
@@ -3004,7 +3016,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -3033,7 +3045,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3062,11 +3074,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>71.72622680664062</v>
+        <v>71.72623443603516</v>
       </c>
       <c r="C106" t="n">
         <v>119.3199996948242</v>
@@ -3091,11 +3103,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>72.10493469238281</v>
+        <v>72.10495758056641</v>
       </c>
       <c r="C107" t="n">
         <v>119.9499969482422</v>
@@ -3120,11 +3132,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>66.05137634277344</v>
+        <v>66.05138397216797</v>
       </c>
       <c r="C108" t="n">
         <v>108.870002746582</v>
@@ -3149,11 +3161,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.05953979492188</v>
+        <v>68.0595703125</v>
       </c>
       <c r="C109" t="n">
         <v>112.1800003051758</v>
@@ -3178,7 +3190,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3207,11 +3219,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>65.35859680175781</v>
+        <v>65.35862731933594</v>
       </c>
       <c r="C111" t="n">
         <v>106.6800003051758</v>
@@ -3236,11 +3248,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>64.31708526611328</v>
+        <v>64.31707000732422</v>
       </c>
       <c r="C112" t="n">
         <v>104.9800033569336</v>
@@ -3265,11 +3277,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.04206848144531</v>
+        <v>68.04205322265625</v>
       </c>
       <c r="C113" t="n">
         <v>111.0599975585938</v>
@@ -3294,11 +3306,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>63.73281097412109</v>
+        <v>63.73280334472656</v>
       </c>
       <c r="C114" t="n">
         <v>103</v>
@@ -3323,11 +3335,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>59.69230270385742</v>
+        <v>59.69228363037109</v>
       </c>
       <c r="C115" t="n">
         <v>96.47000122070312</v>
@@ -3352,11 +3364,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>54.74835586547852</v>
+        <v>54.74835968017578</v>
       </c>
       <c r="C116" t="n">
         <v>88.48000335693359</v>
@@ -3381,11 +3393,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>50.74523162841797</v>
+        <v>50.7452278137207</v>
       </c>
       <c r="C117" t="n">
         <v>80.98999786376953</v>
@@ -3410,11 +3422,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>49.42318725585938</v>
+        <v>49.42316818237305</v>
       </c>
       <c r="C118" t="n">
         <v>78.87999725341797</v>
@@ -3439,7 +3451,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3468,11 +3480,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>57.91642761230469</v>
+        <v>57.91641998291016</v>
       </c>
       <c r="C120" t="n">
         <v>91.31999969482422</v>
@@ -3497,11 +3509,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>57.05387878417969</v>
+        <v>57.05387115478516</v>
       </c>
       <c r="C121" t="n">
         <v>89.95999908447266</v>
@@ -3526,11 +3538,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.84050369262695</v>
+        <v>54.8404655456543</v>
       </c>
       <c r="C122" t="n">
         <v>86.47000122070312</v>
@@ -3555,11 +3567,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.59003067016602</v>
+        <v>53.59001541137695</v>
       </c>
       <c r="C123" t="n">
         <v>83.44000244140625</v>
@@ -3584,11 +3596,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>61.27145385742188</v>
+        <v>61.27143859863281</v>
       </c>
       <c r="C124" t="n">
         <v>95.40000152587891</v>
@@ -3613,11 +3625,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>65.62595367431641</v>
+        <v>65.62596130371094</v>
       </c>
       <c r="C125" t="n">
         <v>102.1800003051758</v>
@@ -3642,11 +3654,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>65.55379486083984</v>
+        <v>65.55378723144531</v>
       </c>
       <c r="C126" t="n">
         <v>101</v>
@@ -3671,11 +3683,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>68.03966522216797</v>
+        <v>68.03964996337891</v>
       </c>
       <c r="C127" t="n">
         <v>104.8300018310547</v>
@@ -3700,11 +3712,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>66.514404296875</v>
+        <v>66.51438903808594</v>
       </c>
       <c r="C128" t="n">
         <v>102.4800033569336</v>
@@ -3729,11 +3741,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>65.96904754638672</v>
+        <v>65.96907043457031</v>
       </c>
       <c r="C129" t="n">
         <v>100.5800018310547</v>
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3783,11 +3795,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>68.7041015625</v>
+        <v>68.70408630371094</v>
       </c>
       <c r="C131" t="n">
         <v>104.75</v>
@@ -3810,11 +3822,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>73.90321350097656</v>
+        <v>73.90318298339844</v>
       </c>
       <c r="C132" t="n">
         <v>111.5599975585938</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>77.97064971923828</v>
+        <v>77.97067260742188</v>
       </c>
       <c r="C133" t="n">
         <v>117.6999969482422</v>
@@ -3864,7 +3876,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>75.23928070068359</v>
+        <v>75.23925018310547</v>
       </c>
       <c r="C135" t="n">
         <v>112.5</v>
@@ -3918,11 +3930,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>71.80835723876953</v>
+        <v>71.80836486816406</v>
       </c>
       <c r="C136" t="n">
         <v>107.370002746582</v>
@@ -3945,11 +3957,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.36026763916016</v>
+        <v>71.36025238037109</v>
       </c>
       <c r="C137" t="n">
         <v>106.6999969482422</v>
@@ -3972,11 +3984,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>69.91075134277344</v>
+        <v>69.91074371337891</v>
       </c>
       <c r="C138" t="n">
         <v>103.4800033569336</v>
@@ -4001,7 +4013,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -4030,11 +4042,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>73.76840209960938</v>
+        <v>73.76840972900391</v>
       </c>
       <c r="C140" t="n">
         <v>109.1900024414062</v>
@@ -4059,11 +4071,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>73.43822479248047</v>
+        <v>73.43824005126953</v>
       </c>
       <c r="C141" t="n">
         <v>107.620002746582</v>
@@ -4088,11 +4100,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>80.18018341064453</v>
+        <v>80.18019104003906</v>
       </c>
       <c r="C142" t="n">
         <v>117.5</v>
@@ -4117,11 +4129,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>79.08153533935547</v>
+        <v>79.08157348632812</v>
       </c>
       <c r="C143" t="n">
         <v>115.8899993896484</v>
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>81.95705413818359</v>
+        <v>81.95706176757812</v>
       </c>
       <c r="C144" t="n">
         <v>118.9899978637695</v>
@@ -4175,11 +4187,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>86.22744750976562</v>
+        <v>86.22746276855469</v>
       </c>
       <c r="C145" t="n">
         <v>125.1900024414062</v>
@@ -4204,11 +4216,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.33763122558594</v>
+        <v>86.33765411376953</v>
       </c>
       <c r="C146" t="n">
         <v>125.3499984741211</v>
@@ -4233,11 +4245,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>77.85480499267578</v>
+        <v>77.85479736328125</v>
       </c>
       <c r="C147" t="n">
         <v>111.9199981689453</v>
@@ -4262,11 +4274,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>79.32954406738281</v>
+        <v>79.32955169677734</v>
       </c>
       <c r="C148" t="n">
         <v>114.0400009155273</v>
@@ -4291,7 +4303,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4320,11 +4332,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>87.22068786621094</v>
+        <v>87.22069549560547</v>
       </c>
       <c r="C150" t="n">
         <v>124.3000030517578</v>
@@ -4349,7 +4361,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4378,11 +4390,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>88.60304260253906</v>
+        <v>88.60301208496094</v>
       </c>
       <c r="C152" t="n">
         <v>126.2699966430664</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>83.91974639892578</v>
+        <v>83.91972351074219</v>
       </c>
       <c r="C153" t="n">
         <v>118.4599990844727</v>
@@ -4436,11 +4448,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>86.62590026855469</v>
+        <v>86.62589263916016</v>
       </c>
       <c r="C154" t="n">
         <v>122.2799987792969</v>
@@ -4465,7 +4477,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4494,11 +4506,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>85.08324432373047</v>
+        <v>85.08325958251953</v>
       </c>
       <c r="C156" t="n">
         <v>118.9400024414062</v>
@@ -4523,11 +4535,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>77.82249450683594</v>
+        <v>77.82247161865234</v>
       </c>
       <c r="C157" t="n">
         <v>108.7900009155273</v>
@@ -4552,11 +4564,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>82.01441955566406</v>
+        <v>82.01439666748047</v>
       </c>
       <c r="C158" t="n">
         <v>114.6500015258789</v>
@@ -4581,11 +4593,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>86.40095520019531</v>
+        <v>86.40097808837891</v>
       </c>
       <c r="C159" t="n">
         <v>119.5800018310547</v>
@@ -4610,11 +4622,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>89.00209045410156</v>
+        <v>89.00210571289062</v>
       </c>
       <c r="C160" t="n">
         <v>123.1800003051758</v>
@@ -4639,11 +4651,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>86.74779510498047</v>
+        <v>86.74777221679688</v>
       </c>
       <c r="C161" t="n">
         <v>120.0599975585938</v>
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4697,11 +4709,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>90.79711151123047</v>
+        <v>90.797119140625</v>
       </c>
       <c r="C163" t="n">
         <v>124.4400024414062</v>
@@ -4726,7 +4738,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4755,7 +4767,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4784,11 +4796,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>87.42555999755859</v>
+        <v>87.42556762695312</v>
       </c>
       <c r="C166" t="n">
         <v>118.5999984741211</v>
@@ -4813,11 +4825,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>85.61219787597656</v>
+        <v>85.61219024658203</v>
       </c>
       <c r="C167" t="n">
         <v>116.1399993896484</v>
@@ -4842,11 +4854,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>87.19272613525391</v>
+        <v>87.19271087646484</v>
       </c>
       <c r="C168" t="n">
         <v>117.129997253418</v>
@@ -4871,11 +4883,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>89.70882415771484</v>
+        <v>89.70883941650391</v>
       </c>
       <c r="C169" t="n">
         <v>120.5100021362305</v>
@@ -4900,7 +4912,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4929,11 +4941,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>70.29533386230469</v>
+        <v>70.29532623291016</v>
       </c>
       <c r="C171" t="n">
         <v>93.33999633789062</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>54.57039260864258</v>
+        <v>54.57037734985352</v>
       </c>
       <c r="C172" t="n">
         <v>72.45999908447266</v>
@@ -4987,11 +4999,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>69.28617095947266</v>
+        <v>69.28615570068359</v>
       </c>
       <c r="C173" t="n">
         <v>92</v>
@@ -5016,11 +5028,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>70.0740966796875</v>
+        <v>70.07408142089844</v>
       </c>
       <c r="C174" t="n">
         <v>91.69999694824219</v>
@@ -5045,11 +5057,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>68.18660736083984</v>
+        <v>68.18659210205078</v>
       </c>
       <c r="C175" t="n">
         <v>89.23000335693359</v>
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>64.14413452148438</v>
+        <v>64.14417266845703</v>
       </c>
       <c r="C176" t="n">
         <v>83.94000244140625</v>
@@ -5103,7 +5115,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>55.81321334838867</v>
+        <v>55.81320953369141</v>
       </c>
       <c r="C178" t="n">
         <v>72</v>
@@ -5157,11 +5169,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>53.8752326965332</v>
+        <v>53.875244140625</v>
       </c>
       <c r="C179" t="n">
         <v>69.5</v>
@@ -5184,11 +5196,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>68.57489013671875</v>
+        <v>68.57489776611328</v>
       </c>
       <c r="C180" t="n">
         <v>87.18000030517578</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>66.42749786376953</v>
+        <v>66.42751312255859</v>
       </c>
       <c r="C181" t="n">
         <v>84.44999694824219</v>
@@ -5238,11 +5250,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>67.01742553710938</v>
+        <v>67.01744079589844</v>
       </c>
       <c r="C182" t="n">
         <v>85.19999694824219</v>
@@ -5265,11 +5277,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>79.77085113525391</v>
+        <v>79.77086639404297</v>
       </c>
       <c r="C183" t="n">
         <v>100</v>
@@ -5292,11 +5304,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>83.59188079833984</v>
+        <v>83.59187316894531</v>
       </c>
       <c r="C184" t="n">
         <v>104.7900009155273</v>
@@ -5319,11 +5331,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>82.21981048583984</v>
+        <v>82.21983337402344</v>
       </c>
       <c r="C185" t="n">
         <v>103.0699996948242</v>
@@ -5346,11 +5358,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>83.80762481689453</v>
+        <v>83.8076171875</v>
       </c>
       <c r="C186" t="n">
         <v>103.7900009155273</v>
@@ -5373,11 +5385,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>84.57474517822266</v>
+        <v>84.57472991943359</v>
       </c>
       <c r="C187" t="n">
         <v>104.7399978637695</v>
@@ -5400,7 +5412,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5427,11 +5439,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>79.19265747070312</v>
+        <v>79.19264984130859</v>
       </c>
       <c r="C189" t="n">
         <v>96.76999664306641</v>
@@ -5456,11 +5468,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>83.02256774902344</v>
+        <v>83.02260589599609</v>
       </c>
       <c r="C190" t="n">
         <v>101.4499969482422</v>
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5543,11 +5555,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>97.14443969726562</v>
+        <v>97.14443206787109</v>
       </c>
       <c r="C193" t="n">
         <v>117.3499984741211</v>
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5601,11 +5613,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>120.4573669433594</v>
+        <v>120.4573364257812</v>
       </c>
       <c r="C195" t="n">
         <v>144</v>
@@ -5630,11 +5642,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>136.2088317871094</v>
+        <v>136.2088012695312</v>
       </c>
       <c r="C196" t="n">
         <v>162.8300018310547</v>
@@ -5659,11 +5671,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>131.0559387207031</v>
+        <v>131.0559234619141</v>
       </c>
       <c r="C197" t="n">
         <v>156.6699981689453</v>
@@ -5688,11 +5700,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>147.3066864013672</v>
+        <v>147.3066558837891</v>
       </c>
       <c r="C198" t="n">
         <v>174.6600036621094</v>
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5746,11 +5758,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>138.1305694580078</v>
+        <v>138.1305541992188</v>
       </c>
       <c r="C200" t="n">
         <v>163.7799987792969</v>
@@ -5775,11 +5787,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>134.5176086425781</v>
+        <v>134.5176239013672</v>
       </c>
       <c r="C201" t="n">
         <v>158.0599975585938</v>
@@ -5804,11 +5816,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>122.2709350585938</v>
+        <v>122.2709579467773</v>
       </c>
       <c r="C202" t="n">
         <v>143.6699981689453</v>
@@ -5833,11 +5845,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>153.9557037353516</v>
+        <v>153.9556884765625</v>
       </c>
       <c r="C203" t="n">
         <v>180.8999938964844</v>
@@ -5862,11 +5874,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>157.2135162353516</v>
+        <v>157.2135467529297</v>
       </c>
       <c r="C204" t="n">
         <v>183.3099975585938</v>
@@ -5891,11 +5903,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>153.9373474121094</v>
+        <v>153.9373626708984</v>
       </c>
       <c r="C205" t="n">
         <v>179.4900054931641</v>
@@ -5920,11 +5932,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>149.2460632324219</v>
+        <v>149.2460784912109</v>
       </c>
       <c r="C206" t="n">
         <v>174.0200042724609</v>
@@ -5949,11 +5961,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>139.1013488769531</v>
+        <v>139.1013031005859</v>
       </c>
       <c r="C207" t="n">
         <v>160.7700042724609</v>
@@ -5978,11 +5990,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>141.1691741943359</v>
+        <v>141.1692047119141</v>
       </c>
       <c r="C208" t="n">
         <v>163.1600036621094</v>
@@ -6007,11 +6019,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>145.858642578125</v>
+        <v>145.8586730957031</v>
       </c>
       <c r="C209" t="n">
         <v>168.5800018310547</v>
@@ -6036,11 +6048,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>131.5954742431641</v>
+        <v>131.5954895019531</v>
       </c>
       <c r="C210" t="n">
         <v>150.6199951171875</v>
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6094,11 +6106,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>142.9883880615234</v>
+        <v>142.9884338378906</v>
       </c>
       <c r="C212" t="n">
         <v>163.6600036621094</v>
@@ -6123,11 +6135,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.1044464111328</v>
+        <v>142.1044769287109</v>
       </c>
       <c r="C213" t="n">
         <v>161.1000061035156</v>
@@ -6152,11 +6164,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>148.7377471923828</v>
+        <v>148.7377319335938</v>
       </c>
       <c r="C214" t="n">
         <v>168.6199951171875</v>
@@ -6181,11 +6193,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>128.5467681884766</v>
+        <v>128.5467529296875</v>
       </c>
       <c r="C215" t="n">
         <v>145.7299957275391</v>
@@ -6210,11 +6222,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>127.9956817626953</v>
+        <v>127.9956893920898</v>
       </c>
       <c r="C216" t="n">
         <v>143.6000061035156</v>
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6268,11 +6280,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>131.4095001220703</v>
+        <v>131.4094848632812</v>
       </c>
       <c r="C218" t="n">
         <v>147.4299926757812</v>
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6355,11 +6367,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>145.3141021728516</v>
+        <v>145.3141174316406</v>
       </c>
       <c r="C221" t="n">
         <v>161.2700042724609</v>
@@ -6384,11 +6396,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>147.7189025878906</v>
+        <v>147.7189331054688</v>
       </c>
       <c r="C222" t="n">
         <v>162.3000030517578</v>
@@ -6413,11 +6425,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>142.3672027587891</v>
+        <v>142.3671875</v>
       </c>
       <c r="C223" t="n">
         <v>156.4199981689453</v>
@@ -6442,11 +6454,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>146.0533447265625</v>
+        <v>146.0533294677734</v>
       </c>
       <c r="C224" t="n">
         <v>160.4700012207031</v>
@@ -6471,11 +6483,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>136.1652374267578</v>
+        <v>136.1652221679688</v>
       </c>
       <c r="C225" t="n">
         <v>147.9499969482422</v>
@@ -6500,11 +6512,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>135.5394134521484</v>
+        <v>135.5393829345703</v>
       </c>
       <c r="C226" t="n">
         <v>147.2700042724609</v>
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6558,11 +6570,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>150.5519256591797</v>
+        <v>150.5519409179688</v>
       </c>
       <c r="C228" t="n">
         <v>161.9299926757812</v>
@@ -6587,11 +6599,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>134.6627655029297</v>
+        <v>134.6627502441406</v>
       </c>
       <c r="C229" t="n">
         <v>144.8399963378906</v>
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6645,11 +6657,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>149.1102142333984</v>
+        <v>149.1102447509766</v>
       </c>
       <c r="C231" t="n">
         <v>158.6199951171875</v>
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6732,11 +6744,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>130.0696258544922</v>
+        <v>130.0696411132812</v>
       </c>
       <c r="C234" t="n">
         <v>136.6999969482422</v>
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6819,11 +6831,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>154.5115356445312</v>
+        <v>154.5115203857422</v>
       </c>
       <c r="C237" t="n">
         <v>160.6000061035156</v>
@@ -6848,11 +6860,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>149.4028015136719</v>
+        <v>149.4028167724609</v>
       </c>
       <c r="C238" t="n">
         <v>155.2899932861328</v>
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7196,32 +7208,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>205.5099945068359</v>
+        <v>205.6499938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>205.5099945068359</v>
+        <v>205.6499938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>168278100</v>
+        <v>177660900</v>
       </c>
       <c r="E250" t="n">
         <v>10.4</v>
       </c>
       <c r="F250" t="n">
-        <v>19.76057639488807</v>
+        <v>19.77403787466196</v>
       </c>
       <c r="G250" t="n">
         <v>1975771274</v>
       </c>
       <c r="H250" t="n">
-        <v>406040743666.5043</v>
+        <v>406317350438.9492</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08517084047857253</v>
+        <v>0.08991977074366554</v>
       </c>
     </row>
   </sheetData>
@@ -7253,75 +7265,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39940</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7474,7 +7486,7 @@
       <c r="I5" t="n">
         <v>11.67</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="K5" t="n">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>39940</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7520,7 +7532,7 @@
       <c r="I6" t="n">
         <v>10.11</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="K6" t="n">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7566,7 +7578,7 @@
       <c r="I7" t="n">
         <v>8.08</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="K7" t="n">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I8" t="n">
         <v>6.15</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="K8" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I9" t="n">
         <v>5.24</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="K9" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I10" t="n">
         <v>6.59</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="K10" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I11" t="n">
         <v>8.42</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="K11" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I12" t="n">
         <v>8.370000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="K12" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I13" t="n">
         <v>9.48</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K13" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I14" t="n">
         <v>10.3</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K14" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I15" t="n">
         <v>11.45</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K15" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I16" t="n">
         <v>13.5</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K16" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I17" t="n">
         <v>13.44</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K17" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I18" t="n">
         <v>13.62</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K18" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I19" t="n">
         <v>13.43</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K19" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I20" t="n">
         <v>12.2</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K20" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I21" t="n">
         <v>13.32</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K21" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I22" t="n">
         <v>13.23</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K22" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I23" t="n">
         <v>12.34</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K23" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I24" t="n">
         <v>12.22</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K24" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I25" t="n">
         <v>11.09</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K25" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I26" t="n">
         <v>10.27</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K26" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I27" t="n">
         <v>10.48</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K27" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I28" t="n">
         <v>10.86</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K28" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I29" t="n">
         <v>10.14</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K29" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I30" t="n">
         <v>9.150000000000002</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K30" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I31" t="n">
         <v>6.470000000000002</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K31" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I32" t="n">
         <v>4.610000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K32" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I33" t="n">
         <v>2.45</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K33" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I34" t="n">
         <v>0.6900000000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K34" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I35" t="n">
         <v>-0.39</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K35" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I36" t="n">
         <v>-0.7999999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K36" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I37" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K37" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I38" t="n">
         <v>1.53</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K38" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I39" t="n">
         <v>3.08</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K39" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I40" t="n">
         <v>3.43</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K40" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I41" t="n">
         <v>4.85</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K41" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I42" t="n">
         <v>5.34</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K42" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I43" t="n">
         <v>6.350000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K43" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I44" t="n">
         <v>7.43</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="K44" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I45" t="n">
         <v>7.740000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K45" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I46" t="n">
         <v>7.23</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K46" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I47" t="n">
         <v>7.720000000000002</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K47" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I48" t="n">
         <v>6.970000000000002</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K48" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I49" t="n">
         <v>1.54</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K49" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I50" t="n">
         <v>2.08</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K50" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I51" t="n">
         <v>-4.630000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K51" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I52" t="n">
         <v>-6.11</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K52" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I53" t="n">
         <v>-2.959999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K53" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I54" t="n">
         <v>-4.169999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K54" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I55" t="n">
         <v>1.870000000000002</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K55" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I56" t="n">
         <v>5.180000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K56" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I57" t="n">
         <v>8.140000000000002</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K57" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I58" t="n">
         <v>10.64</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K58" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I59" t="n">
         <v>14.99</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K59" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I60" t="n">
         <v>17.58</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K60" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I61" t="n">
         <v>18.28</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K61" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I62" t="n">
         <v>18.52</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K62" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I63" t="n">
         <v>15.77</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K63" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I64" t="n">
         <v>13.47</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K64" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I65" t="n">
         <v>11.36</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K65" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I66" t="n">
         <v>10.87</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K66" t="n">
@@ -10293,13 +10305,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10326,7 +10338,7 @@
       <c r="I67" t="n">
         <v>10.1</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K67" t="n">
@@ -10339,13 +10351,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10372,7 +10384,7 @@
       <c r="I68" t="n">
         <v>9.1</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K68" t="n">
@@ -10385,13 +10397,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10418,7 +10430,7 @@
       <c r="I69" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K69" t="n">
@@ -10431,13 +10443,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10464,7 +10476,7 @@
       <c r="I70" t="n">
         <v>8.75</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="K70" t="n">
@@ -10477,13 +10489,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10510,7 +10522,7 @@
       <c r="I71" t="n">
         <v>7.770000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K71" t="n">
@@ -10523,13 +10535,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10556,7 +10568,7 @@
       <c r="I72" t="n">
         <v>7.110000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K72" t="n">
@@ -10569,13 +10581,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10602,7 +10614,7 @@
       <c r="I73" t="n">
         <v>6.630000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K73" t="n">
@@ -10615,13 +10627,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10648,7 +10660,7 @@
       <c r="I74" t="n">
         <v>5.74</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K74" t="n">
@@ -10661,13 +10673,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10694,7 +10706,7 @@
       <c r="I75" t="n">
         <v>10.4</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K75" t="n">
@@ -10731,52 +10743,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39940</v>
       </c>
       <c r="C2" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C3" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C4" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40228</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C5" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C6" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C7" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C8" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C9" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C10" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C11" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C12" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40952</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C13" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C14" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C15" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C16" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41316</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C17" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C18" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C19" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C20" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41680</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C21" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C22" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C23" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C24" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42044</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C25" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C26" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C27" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C28" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42415</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C29" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C30" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C31" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C32" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42781</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C33" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C34" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C35" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C36" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43143</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C37" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C38" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C39" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="C40" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43507</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C41" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C42" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C43" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C44" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C45" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C46" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C47" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C48" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C49" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C50" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C51" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C52" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44602</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C53" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C54" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C55" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C56" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C57" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C58" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C59" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C60" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C61" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C62" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C63" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C64" t="n">
@@ -12789,10 +12801,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C65" t="n">
@@ -12821,10 +12833,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="C66" t="n">
@@ -12853,10 +12865,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C67" t="n">
@@ -12885,10 +12897,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C68" t="n">
@@ -12917,10 +12929,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C69" t="n">
@@ -12949,10 +12961,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C70" t="n">
@@ -12981,10 +12993,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C71" t="n">
@@ -13031,12 +13043,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CVX.xlsx
+++ b/salidas/empresas/CVX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.80402946472168</v>
+        <v>26.80403137207031</v>
       </c>
       <c r="C2" t="n">
         <v>59.38000106811523</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.6992244720459</v>
+        <v>25.6992301940918</v>
       </c>
       <c r="C3" t="n">
         <v>56.47999954223633</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.37719535827637</v>
+        <v>26.37720489501953</v>
       </c>
       <c r="C4" t="n">
         <v>57.97000122070312</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.76499176025391</v>
+        <v>27.76499938964844</v>
       </c>
       <c r="C5" t="n">
         <v>61.02000045776367</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.43915176391602</v>
+        <v>27.43917274475098</v>
       </c>
       <c r="C6" t="n">
         <v>59.79000091552734</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.48091125488281</v>
+        <v>28.48092842102051</v>
       </c>
       <c r="C7" t="n">
         <v>62.06000137329102</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>30.18811416625977</v>
+        <v>30.18811988830566</v>
       </c>
       <c r="C8" t="n">
         <v>65.77999877929688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.78647041320801</v>
+        <v>29.78647804260254</v>
       </c>
       <c r="C9" t="n">
         <v>64.40000152587891</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.99923133850098</v>
+        <v>29.99923706054688</v>
       </c>
       <c r="C10" t="n">
         <v>64.86000061035156</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.0815315246582</v>
+        <v>31.08154678344727</v>
       </c>
       <c r="C11" t="n">
         <v>67.19999694824219</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>34.262451171875</v>
+        <v>34.26243209838867</v>
       </c>
       <c r="C13" t="n">
         <v>73.52999877929688</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>33.95957565307617</v>
+        <v>33.95956802368164</v>
       </c>
       <c r="C14" t="n">
         <v>72.87999725341797</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.15755844116211</v>
+        <v>32.15754699707031</v>
       </c>
       <c r="C15" t="n">
         <v>68.51999664306641</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>34.71063995361328</v>
+        <v>34.71065521240234</v>
       </c>
       <c r="C16" t="n">
         <v>73.95999908447266</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.50812911987305</v>
+        <v>36.50814056396484</v>
       </c>
       <c r="C17" t="n">
         <v>77.79000091552734</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.52134323120117</v>
+        <v>38.5213508605957</v>
       </c>
       <c r="C18" t="n">
         <v>81.48999786376953</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>39.82129669189453</v>
+        <v>39.82131576538086</v>
       </c>
       <c r="C19" t="n">
         <v>84.23999786376953</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>40.30348587036133</v>
+        <v>40.30347442626953</v>
       </c>
       <c r="C20" t="n">
         <v>85.26000213623047</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>41.77913665771484</v>
+        <v>41.77915573120117</v>
       </c>
       <c r="C21" t="n">
         <v>87.76000213623047</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>44.54983520507812</v>
+        <v>44.54981231689453</v>
       </c>
       <c r="C22" t="n">
         <v>93.58000183105469</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>43.56438827514648</v>
+        <v>43.56439208984375</v>
       </c>
       <c r="C23" t="n">
         <v>91.51000213623047</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>42.06490325927734</v>
+        <v>42.06489562988281</v>
       </c>
       <c r="C24" t="n">
         <v>87.76999664306641</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>44.72962188720703</v>
+        <v>44.7296257019043</v>
       </c>
       <c r="C25" t="n">
         <v>93.33000183105469</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.89863586425781</v>
+        <v>39.89862060546875</v>
       </c>
       <c r="C26" t="n">
         <v>83.25</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>41.83202362060547</v>
+        <v>41.83201599121094</v>
       </c>
       <c r="C27" t="n">
         <v>86.66000366210938</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>48.18159484863281</v>
+        <v>48.18161773681641</v>
       </c>
       <c r="C30" t="n">
         <v>99.15000152587891</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.171875</v>
+        <v>48.17188262939453</v>
       </c>
       <c r="C31" t="n">
         <v>99.12999725341797</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.09164047241211</v>
+        <v>41.09164428710938</v>
       </c>
       <c r="C32" t="n">
         <v>84.55999755859375</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>42.26419448852539</v>
+        <v>42.26418304443359</v>
       </c>
       <c r="C33" t="n">
         <v>86.31999969482422</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.38405609130859</v>
+        <v>40.38406372070312</v>
       </c>
       <c r="C34" t="n">
         <v>82.48000335693359</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>36.52582931518555</v>
+        <v>36.52582168579102</v>
       </c>
       <c r="C35" t="n">
         <v>74.59999847412109</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>39.02006149291992</v>
+        <v>39.02006530761719</v>
       </c>
       <c r="C36" t="n">
         <v>79.01000213623047</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.53098678588867</v>
+        <v>36.53099822998047</v>
       </c>
       <c r="C37" t="n">
         <v>73.97000122070312</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>34.82716751098633</v>
+        <v>34.82717132568359</v>
       </c>
       <c r="C38" t="n">
         <v>70.51999664306641</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>30.25838279724121</v>
+        <v>30.25839805603027</v>
       </c>
       <c r="C39" t="n">
         <v>60.70999908447266</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.94480895996094</v>
+        <v>32.94480514526367</v>
       </c>
       <c r="C41" t="n">
         <v>66.09999847412109</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>33.55031585693359</v>
+        <v>33.5503044128418</v>
       </c>
       <c r="C42" t="n">
         <v>66.66999816894531</v>
@@ -1283,7 +1283,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>33.33896636962891</v>
+        <v>33.33895874023438</v>
       </c>
       <c r="C43" t="n">
         <v>66.25</v>
@@ -1308,7 +1308,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.9593620300293</v>
+        <v>34.95936584472656</v>
       </c>
       <c r="C44" t="n">
         <v>69.47000122070312</v>
@@ -1333,7 +1333,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>35.548095703125</v>
+        <v>35.54809951782227</v>
       </c>
       <c r="C45" t="n">
         <v>69.94000244140625</v>
@@ -1358,7 +1358,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>35.79714202880859</v>
+        <v>35.79712677001953</v>
       </c>
       <c r="C46" t="n">
         <v>70.43000030517578</v>
@@ -1383,7 +1383,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.90264511108398</v>
+        <v>38.90262603759766</v>
       </c>
       <c r="C47" t="n">
         <v>76.54000091552734</v>
@@ -1408,7 +1408,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.01415252685547</v>
+        <v>40.0141487121582</v>
       </c>
       <c r="C48" t="n">
         <v>78.04000091552734</v>
@@ -1433,7 +1433,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>39.47576904296875</v>
+        <v>39.47576522827148</v>
       </c>
       <c r="C49" t="n">
         <v>76.98999786376953</v>
@@ -1458,7 +1458,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>36.97872161865234</v>
+        <v>36.97874450683594</v>
       </c>
       <c r="C50" t="n">
         <v>72.12000274658203</v>
@@ -1483,7 +1483,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.42581558227539</v>
+        <v>37.42582321166992</v>
       </c>
       <c r="C51" t="n">
         <v>72.30000305175781</v>
@@ -1512,7 +1512,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>39.25313186645508</v>
+        <v>39.25312042236328</v>
       </c>
       <c r="C52" t="n">
         <v>75.83000183105469</v>
@@ -1570,7 +1570,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>38.59557723999023</v>
+        <v>38.5955810546875</v>
       </c>
       <c r="C54" t="n">
         <v>73.87000274658203</v>
@@ -1599,7 +1599,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.45546722412109</v>
+        <v>35.45547485351562</v>
       </c>
       <c r="C55" t="n">
         <v>67.86000061035156</v>
@@ -1628,7 +1628,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.81818389892578</v>
+        <v>39.81818008422852</v>
       </c>
       <c r="C56" t="n">
         <v>76.20999908447266</v>
@@ -1657,7 +1657,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>39.0672721862793</v>
+        <v>39.06726837158203</v>
       </c>
       <c r="C57" t="n">
         <v>74.08000183105469</v>
@@ -1686,7 +1686,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>42.74302291870117</v>
+        <v>42.74300003051758</v>
       </c>
       <c r="C58" t="n">
         <v>81.05000305175781</v>
@@ -1715,7 +1715,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>43.56043243408203</v>
+        <v>43.56041717529297</v>
       </c>
       <c r="C59" t="n">
         <v>82.59999847412109</v>
@@ -1773,7 +1773,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>48.53391265869141</v>
+        <v>48.533935546875</v>
       </c>
       <c r="C61" t="n">
         <v>91.25</v>
@@ -1802,7 +1802,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>50.49124908447266</v>
+        <v>50.49123001098633</v>
       </c>
       <c r="C62" t="n">
         <v>94.93000030517578</v>
@@ -1831,7 +1831,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>55.59743881225586</v>
+        <v>55.59743499755859</v>
       </c>
       <c r="C63" t="n">
         <v>103.75</v>
@@ -1860,7 +1860,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>57.60163879394531</v>
+        <v>57.60165023803711</v>
       </c>
       <c r="C64" t="n">
         <v>107.4899978637695</v>
@@ -1889,7 +1889,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>58.64659881591797</v>
+        <v>58.64662170410156</v>
       </c>
       <c r="C65" t="n">
         <v>109.4400024414062</v>
@@ -1976,7 +1976,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.17317962646484</v>
+        <v>56.17317199707031</v>
       </c>
       <c r="C68" t="n">
         <v>104.0199966430664</v>
@@ -2005,7 +2005,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.8034782409668</v>
+        <v>53.80348205566406</v>
       </c>
       <c r="C69" t="n">
         <v>98.83999633789062</v>
@@ -2034,7 +2034,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>50.40127182006836</v>
+        <v>50.40130233764648</v>
       </c>
       <c r="C70" t="n">
         <v>92.58999633789062</v>
@@ -2092,7 +2092,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>56.41243743896484</v>
+        <v>56.41244125366211</v>
       </c>
       <c r="C72" t="n">
         <v>102.8199996948242</v>
@@ -2121,7 +2121,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>58.37663269042969</v>
+        <v>58.37661361694336</v>
       </c>
       <c r="C73" t="n">
         <v>106.4000015258789</v>
@@ -2150,7 +2150,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>56.57705307006836</v>
+        <v>56.57705688476562</v>
       </c>
       <c r="C74" t="n">
         <v>103.120002746582</v>
@@ -2179,7 +2179,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>60.32784652709961</v>
+        <v>60.32783508300781</v>
       </c>
       <c r="C75" t="n">
         <v>109.120002746582</v>
@@ -2208,7 +2208,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.27187347412109</v>
+        <v>59.2718620300293</v>
       </c>
       <c r="C76" t="n">
         <v>107.2099990844727</v>
@@ -2237,7 +2237,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>58.91250610351562</v>
+        <v>58.91252517700195</v>
       </c>
       <c r="C77" t="n">
         <v>106.5599975585938</v>
@@ -2266,7 +2266,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>54.84059524536133</v>
+        <v>54.84060287475586</v>
       </c>
       <c r="C78" t="n">
         <v>98.30999755859375</v>
@@ -2295,7 +2295,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>58.85143280029297</v>
+        <v>58.85142135620117</v>
       </c>
       <c r="C79" t="n">
         <v>105.5</v>
@@ -2324,7 +2324,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>61.12743377685547</v>
+        <v>61.12740707397461</v>
       </c>
       <c r="C80" t="n">
         <v>109.5800018310547</v>
@@ -2353,7 +2353,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>63.06747436523438</v>
+        <v>63.06748199462891</v>
       </c>
       <c r="C81" t="n">
         <v>112.1600036621094</v>
@@ -2382,7 +2382,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>65.54158020019531</v>
+        <v>65.54161834716797</v>
       </c>
       <c r="C82" t="n">
         <v>116.5599975585938</v>
@@ -2440,7 +2440,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>59.94186019897461</v>
+        <v>59.94182968139648</v>
       </c>
       <c r="C84" t="n">
         <v>105.6900024414062</v>
@@ -2469,7 +2469,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.33133316040039</v>
+        <v>61.33135604858398</v>
       </c>
       <c r="C85" t="n">
         <v>108.1399993896484</v>
@@ -2498,7 +2498,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>65.30706024169922</v>
+        <v>65.30706787109375</v>
       </c>
       <c r="C86" t="n">
         <v>115.1500015258789</v>
@@ -2556,7 +2556,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>67.91313934326172</v>
+        <v>67.91311645507812</v>
       </c>
       <c r="C88" t="n">
         <v>118.8199996948242</v>
@@ -2585,7 +2585,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.73641967773438</v>
+        <v>69.73641204833984</v>
       </c>
       <c r="C89" t="n">
         <v>122.0100021362305</v>
@@ -2614,7 +2614,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>70.72517395019531</v>
+        <v>70.72518157958984</v>
       </c>
       <c r="C90" t="n">
         <v>122.75</v>
@@ -2643,7 +2643,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>68.18426513671875</v>
+        <v>68.18427276611328</v>
       </c>
       <c r="C91" t="n">
         <v>118.3399963378906</v>
@@ -2701,7 +2701,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>69.961669921875</v>
+        <v>69.96168518066406</v>
       </c>
       <c r="C93" t="n">
         <v>120.4300003051758</v>
@@ -2730,7 +2730,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>70.58328247070312</v>
+        <v>70.58327484130859</v>
       </c>
       <c r="C94" t="n">
         <v>121.5</v>
@@ -2759,7 +2759,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>69.68865203857422</v>
+        <v>69.68863677978516</v>
       </c>
       <c r="C95" t="n">
         <v>119.9599990844727</v>
@@ -2788,7 +2788,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>71.72663116455078</v>
+        <v>71.72662353515625</v>
       </c>
       <c r="C96" t="n">
         <v>122.4400024414062</v>
@@ -2817,7 +2817,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>73.17356109619141</v>
+        <v>73.17357635498047</v>
       </c>
       <c r="C97" t="n">
         <v>124.9100036621094</v>
@@ -2846,7 +2846,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>65.39399719238281</v>
+        <v>65.39401245117188</v>
       </c>
       <c r="C98" t="n">
         <v>111.629997253418</v>
@@ -2875,7 +2875,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.16160583496094</v>
+        <v>68.16162872314453</v>
       </c>
       <c r="C99" t="n">
         <v>115.3300018310547</v>
@@ -2904,7 +2904,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>70.27743530273438</v>
+        <v>70.27747344970703</v>
       </c>
       <c r="C100" t="n">
         <v>118.9100036621094</v>
@@ -2933,7 +2933,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>74.18405151367188</v>
+        <v>74.18405914306641</v>
       </c>
       <c r="C101" t="n">
         <v>125.5199966430664</v>
@@ -2962,7 +2962,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.1900634765625</v>
+        <v>73.19005584716797</v>
       </c>
       <c r="C102" t="n">
         <v>122.7900009155273</v>
@@ -2991,7 +2991,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>77.81549072265625</v>
+        <v>77.81548309326172</v>
       </c>
       <c r="C103" t="n">
         <v>130.5500030517578</v>
@@ -3020,7 +3020,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>77.03465270996094</v>
+        <v>77.03464508056641</v>
       </c>
       <c r="C104" t="n">
         <v>129.2400054931641</v>
@@ -3078,7 +3078,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>71.72623443603516</v>
+        <v>71.72621917724609</v>
       </c>
       <c r="C106" t="n">
         <v>119.3199996948242</v>
@@ -3107,7 +3107,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>72.10495758056641</v>
+        <v>72.10494232177734</v>
       </c>
       <c r="C107" t="n">
         <v>119.9499969482422</v>
@@ -3136,7 +3136,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>66.05138397216797</v>
+        <v>66.0513916015625</v>
       </c>
       <c r="C108" t="n">
         <v>108.870002746582</v>
@@ -3165,7 +3165,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.0595703125</v>
+        <v>68.05960083007812</v>
       </c>
       <c r="C109" t="n">
         <v>112.1800003051758</v>
@@ -3194,7 +3194,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>62.20492553710938</v>
+        <v>62.2049446105957</v>
       </c>
       <c r="C110" t="n">
         <v>102.5299987792969</v>
@@ -3223,7 +3223,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>65.35862731933594</v>
+        <v>65.35857391357422</v>
       </c>
       <c r="C111" t="n">
         <v>106.6800003051758</v>
@@ -3281,7 +3281,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.04205322265625</v>
+        <v>68.04206085205078</v>
       </c>
       <c r="C113" t="n">
         <v>111.0599975585938</v>
@@ -3310,7 +3310,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>63.73280334472656</v>
+        <v>63.7327995300293</v>
       </c>
       <c r="C114" t="n">
         <v>103</v>
@@ -3339,7 +3339,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>59.69228363037109</v>
+        <v>59.69225692749023</v>
       </c>
       <c r="C115" t="n">
         <v>96.47000122070312</v>
@@ -3368,7 +3368,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>54.74835968017578</v>
+        <v>54.74834060668945</v>
       </c>
       <c r="C116" t="n">
         <v>88.48000335693359</v>
@@ -3397,7 +3397,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>50.7452278137207</v>
+        <v>50.7452507019043</v>
       </c>
       <c r="C117" t="n">
         <v>80.98999786376953</v>
@@ -3426,7 +3426,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>49.42316818237305</v>
+        <v>49.42318344116211</v>
       </c>
       <c r="C118" t="n">
         <v>78.87999725341797</v>
@@ -3455,7 +3455,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.94192886352539</v>
+        <v>56.94191360473633</v>
       </c>
       <c r="C119" t="n">
         <v>90.87999725341797</v>
@@ -3513,7 +3513,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>57.05387115478516</v>
+        <v>57.05388259887695</v>
       </c>
       <c r="C121" t="n">
         <v>89.95999908447266</v>
@@ -3542,7 +3542,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.8404655456543</v>
+        <v>54.84049224853516</v>
       </c>
       <c r="C122" t="n">
         <v>86.47000122070312</v>
@@ -3571,7 +3571,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.59001541137695</v>
+        <v>53.59003448486328</v>
       </c>
       <c r="C123" t="n">
         <v>83.44000244140625</v>
@@ -3600,7 +3600,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>61.27143859863281</v>
+        <v>61.27142715454102</v>
       </c>
       <c r="C124" t="n">
         <v>95.40000152587891</v>
@@ -3658,7 +3658,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>65.55378723144531</v>
+        <v>65.55380249023438</v>
       </c>
       <c r="C126" t="n">
         <v>101</v>
@@ -3687,7 +3687,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>68.03964996337891</v>
+        <v>68.0396728515625</v>
       </c>
       <c r="C127" t="n">
         <v>104.8300018310547</v>
@@ -3716,7 +3716,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>66.51438903808594</v>
+        <v>66.51441192626953</v>
       </c>
       <c r="C128" t="n">
         <v>102.4800033569336</v>
@@ -3745,7 +3745,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>65.96907043457031</v>
+        <v>65.96903228759766</v>
       </c>
       <c r="C129" t="n">
         <v>100.5800018310547</v>
@@ -3799,7 +3799,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>68.70408630371094</v>
+        <v>68.70409393310547</v>
       </c>
       <c r="C131" t="n">
         <v>104.75</v>
@@ -3826,7 +3826,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>73.90318298339844</v>
+        <v>73.90322113037109</v>
       </c>
       <c r="C132" t="n">
         <v>111.5599975585938</v>
@@ -3853,7 +3853,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>77.97067260742188</v>
+        <v>77.97064208984375</v>
       </c>
       <c r="C133" t="n">
         <v>117.6999969482422</v>
@@ -3880,7 +3880,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>73.76408386230469</v>
+        <v>73.76409149169922</v>
       </c>
       <c r="C134" t="n">
         <v>111.3499984741211</v>
@@ -3907,7 +3907,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>75.23925018310547</v>
+        <v>75.23927307128906</v>
       </c>
       <c r="C135" t="n">
         <v>112.5</v>
@@ -3934,7 +3934,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>71.80836486816406</v>
+        <v>71.80834197998047</v>
       </c>
       <c r="C136" t="n">
         <v>107.370002746582</v>
@@ -3961,7 +3961,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.36025238037109</v>
+        <v>71.36024475097656</v>
       </c>
       <c r="C137" t="n">
         <v>106.6999969482422</v>
@@ -4046,7 +4046,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>73.76840972900391</v>
+        <v>73.76838684082031</v>
       </c>
       <c r="C140" t="n">
         <v>109.1900024414062</v>
@@ -4075,7 +4075,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>73.43824005126953</v>
+        <v>73.43825531005859</v>
       </c>
       <c r="C141" t="n">
         <v>107.620002746582</v>
@@ -4104,7 +4104,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>80.18019104003906</v>
+        <v>80.18019866943359</v>
       </c>
       <c r="C142" t="n">
         <v>117.5</v>
@@ -4133,7 +4133,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>79.08157348632812</v>
+        <v>79.08154296875</v>
       </c>
       <c r="C143" t="n">
         <v>115.8899993896484</v>
@@ -4162,7 +4162,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>81.95706176757812</v>
+        <v>81.95706939697266</v>
       </c>
       <c r="C144" t="n">
         <v>118.9899978637695</v>
@@ -4191,7 +4191,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>86.22746276855469</v>
+        <v>86.22744750976562</v>
       </c>
       <c r="C145" t="n">
         <v>125.1900024414062</v>
@@ -4220,7 +4220,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.33765411376953</v>
+        <v>86.337646484375</v>
       </c>
       <c r="C146" t="n">
         <v>125.3499984741211</v>
@@ -4249,7 +4249,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>77.85479736328125</v>
+        <v>77.85481262207031</v>
       </c>
       <c r="C147" t="n">
         <v>111.9199981689453</v>
@@ -4307,7 +4307,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>87.03015899658203</v>
+        <v>87.03018188476562</v>
       </c>
       <c r="C149" t="n">
         <v>125.1100006103516</v>
@@ -4336,7 +4336,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>87.22069549560547</v>
+        <v>87.22071838378906</v>
       </c>
       <c r="C150" t="n">
         <v>124.3000030517578</v>
@@ -4394,7 +4394,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>88.60301208496094</v>
+        <v>88.60304260253906</v>
       </c>
       <c r="C152" t="n">
         <v>126.2699966430664</v>
@@ -4423,7 +4423,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>83.91972351074219</v>
+        <v>83.91973876953125</v>
       </c>
       <c r="C153" t="n">
         <v>118.4599990844727</v>
@@ -4481,7 +4481,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>79.09535980224609</v>
+        <v>79.09536743164062</v>
       </c>
       <c r="C155" t="n">
         <v>111.6500015258789</v>
@@ -4510,7 +4510,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>85.08325958251953</v>
+        <v>85.08327484130859</v>
       </c>
       <c r="C156" t="n">
         <v>118.9400024414062</v>
@@ -4539,7 +4539,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>77.82247161865234</v>
+        <v>77.82248687744141</v>
       </c>
       <c r="C157" t="n">
         <v>108.7900009155273</v>
@@ -4568,7 +4568,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>82.01439666748047</v>
+        <v>82.01441192626953</v>
       </c>
       <c r="C158" t="n">
         <v>114.6500015258789</v>
@@ -4597,7 +4597,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>86.40097808837891</v>
+        <v>86.40095520019531</v>
       </c>
       <c r="C159" t="n">
         <v>119.5800018310547</v>
@@ -4626,7 +4626,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>89.00210571289062</v>
+        <v>89.00212097167969</v>
       </c>
       <c r="C160" t="n">
         <v>123.1800003051758</v>
@@ -4684,7 +4684,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>83.07015228271484</v>
+        <v>83.07016754150391</v>
       </c>
       <c r="C162" t="n">
         <v>113.8499984741211</v>
@@ -4742,7 +4742,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>89.82667541503906</v>
+        <v>89.82668304443359</v>
       </c>
       <c r="C164" t="n">
         <v>123.1100006103516</v>
@@ -4771,7 +4771,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>86.77687835693359</v>
+        <v>86.77687072753906</v>
       </c>
       <c r="C165" t="n">
         <v>117.7200012207031</v>
@@ -4800,7 +4800,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>87.42556762695312</v>
+        <v>87.42555999755859</v>
       </c>
       <c r="C166" t="n">
         <v>118.5999984741211</v>
@@ -4829,7 +4829,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>85.61219024658203</v>
+        <v>85.6121826171875</v>
       </c>
       <c r="C167" t="n">
         <v>116.1399993896484</v>
@@ -4858,7 +4858,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>87.19271087646484</v>
+        <v>87.19272613525391</v>
       </c>
       <c r="C168" t="n">
         <v>117.129997253418</v>
@@ -4887,7 +4887,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>89.70883941650391</v>
+        <v>89.70882415771484</v>
       </c>
       <c r="C169" t="n">
         <v>120.5100021362305</v>
@@ -4916,7 +4916,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>79.75606536865234</v>
+        <v>79.75609588623047</v>
       </c>
       <c r="C170" t="n">
         <v>107.1399993896484</v>
@@ -4945,7 +4945,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>70.29532623291016</v>
+        <v>70.29533386230469</v>
       </c>
       <c r="C171" t="n">
         <v>93.33999633789062</v>
@@ -4974,7 +4974,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>54.57037734985352</v>
+        <v>54.57039642333984</v>
       </c>
       <c r="C172" t="n">
         <v>72.45999908447266</v>
@@ -5061,7 +5061,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>68.18659210205078</v>
+        <v>68.18659973144531</v>
       </c>
       <c r="C175" t="n">
         <v>89.23000335693359</v>
@@ -5090,7 +5090,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>64.14417266845703</v>
+        <v>64.14414978027344</v>
       </c>
       <c r="C176" t="n">
         <v>83.94000244140625</v>
@@ -5146,7 +5146,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>55.81320953369141</v>
+        <v>55.81319427490234</v>
       </c>
       <c r="C178" t="n">
         <v>72</v>
@@ -5173,7 +5173,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>53.875244140625</v>
+        <v>53.87525177001953</v>
       </c>
       <c r="C179" t="n">
         <v>69.5</v>
@@ -5200,7 +5200,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>68.57489776611328</v>
+        <v>68.57490539550781</v>
       </c>
       <c r="C180" t="n">
         <v>87.18000030517578</v>
@@ -5227,7 +5227,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>66.42751312255859</v>
+        <v>66.42749786376953</v>
       </c>
       <c r="C181" t="n">
         <v>84.44999694824219</v>
@@ -5254,7 +5254,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>67.01744079589844</v>
+        <v>67.01744842529297</v>
       </c>
       <c r="C182" t="n">
         <v>85.19999694824219</v>
@@ -5281,7 +5281,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>79.77086639404297</v>
+        <v>79.77084350585938</v>
       </c>
       <c r="C183" t="n">
         <v>100</v>
@@ -5308,7 +5308,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>83.59187316894531</v>
+        <v>83.59188079833984</v>
       </c>
       <c r="C184" t="n">
         <v>104.7900009155273</v>
@@ -5335,7 +5335,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>82.21983337402344</v>
+        <v>82.21981811523438</v>
       </c>
       <c r="C185" t="n">
         <v>103.0699996948242</v>
@@ -5389,7 +5389,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>84.57472991943359</v>
+        <v>84.57473754882812</v>
       </c>
       <c r="C187" t="n">
         <v>104.7399978637695</v>
@@ -5416,7 +5416,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>82.20884704589844</v>
+        <v>82.20883178710938</v>
       </c>
       <c r="C188" t="n">
         <v>101.8099975585938</v>
@@ -5443,7 +5443,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>79.19264984130859</v>
+        <v>79.19265747070312</v>
       </c>
       <c r="C189" t="n">
         <v>96.76999664306641</v>
@@ -5472,7 +5472,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>83.02260589599609</v>
+        <v>83.02257537841797</v>
       </c>
       <c r="C190" t="n">
         <v>101.4499969482422</v>
@@ -5501,7 +5501,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>93.69398498535156</v>
+        <v>93.69399261474609</v>
       </c>
       <c r="C191" t="n">
         <v>114.4899978637695</v>
@@ -5530,7 +5530,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>93.43582153320312</v>
+        <v>93.43581390380859</v>
       </c>
       <c r="C192" t="n">
         <v>112.870002746582</v>
@@ -5559,7 +5559,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>97.14443206787109</v>
+        <v>97.14444732666016</v>
       </c>
       <c r="C193" t="n">
         <v>117.3499984741211</v>
@@ -5617,7 +5617,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>120.4573364257812</v>
+        <v>120.4573440551758</v>
       </c>
       <c r="C195" t="n">
         <v>144</v>
@@ -5704,7 +5704,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>147.3066558837891</v>
+        <v>147.306640625</v>
       </c>
       <c r="C198" t="n">
         <v>174.6600036621094</v>
@@ -5762,7 +5762,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>138.1305541992188</v>
+        <v>138.1305694580078</v>
       </c>
       <c r="C200" t="n">
         <v>163.7799987792969</v>
@@ -5820,7 +5820,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>122.2709579467773</v>
+        <v>122.2709884643555</v>
       </c>
       <c r="C202" t="n">
         <v>143.6699981689453</v>
@@ -5878,7 +5878,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>157.2135467529297</v>
+        <v>157.2135162353516</v>
       </c>
       <c r="C204" t="n">
         <v>183.3099975585938</v>
@@ -5936,7 +5936,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>149.2460784912109</v>
+        <v>149.2461090087891</v>
       </c>
       <c r="C206" t="n">
         <v>174.0200042724609</v>
@@ -5965,7 +5965,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>139.1013031005859</v>
+        <v>139.1012878417969</v>
       </c>
       <c r="C207" t="n">
         <v>160.7700042724609</v>
@@ -5994,7 +5994,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>141.1692047119141</v>
+        <v>141.169189453125</v>
       </c>
       <c r="C208" t="n">
         <v>163.1600036621094</v>
@@ -6023,7 +6023,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>145.8586730957031</v>
+        <v>145.858642578125</v>
       </c>
       <c r="C209" t="n">
         <v>168.5800018310547</v>
@@ -6052,7 +6052,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>131.5954895019531</v>
+        <v>131.595458984375</v>
       </c>
       <c r="C210" t="n">
         <v>150.6199951171875</v>
@@ -6081,7 +6081,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>137.4754028320312</v>
+        <v>137.4754180908203</v>
       </c>
       <c r="C211" t="n">
         <v>157.3500061035156</v>
@@ -6110,7 +6110,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>142.9884338378906</v>
+        <v>142.9884033203125</v>
       </c>
       <c r="C212" t="n">
         <v>163.6600036621094</v>
@@ -6139,7 +6139,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.1044769287109</v>
+        <v>142.1044464111328</v>
       </c>
       <c r="C213" t="n">
         <v>161.1000061035156</v>
@@ -6168,7 +6168,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>148.7377319335938</v>
+        <v>148.7377471923828</v>
       </c>
       <c r="C214" t="n">
         <v>168.6199951171875</v>
@@ -6197,7 +6197,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>128.5467529296875</v>
+        <v>128.5467376708984</v>
       </c>
       <c r="C215" t="n">
         <v>145.7299957275391</v>
@@ -6226,7 +6226,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>127.9956893920898</v>
+        <v>127.9957046508789</v>
       </c>
       <c r="C216" t="n">
         <v>143.6000061035156</v>
@@ -6255,7 +6255,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>132.9514923095703</v>
+        <v>132.9515228271484</v>
       </c>
       <c r="C217" t="n">
         <v>149.1600036621094</v>
@@ -6313,7 +6313,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>136.9702758789062</v>
+        <v>136.9702606201172</v>
       </c>
       <c r="C219" t="n">
         <v>152.0099945068359</v>
@@ -6342,7 +6342,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>142.1333770751953</v>
+        <v>142.1333618164062</v>
       </c>
       <c r="C220" t="n">
         <v>157.7400054931641</v>
@@ -6371,7 +6371,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>145.3141174316406</v>
+        <v>145.3141021728516</v>
       </c>
       <c r="C221" t="n">
         <v>161.2700042724609</v>
@@ -6458,7 +6458,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>146.0533294677734</v>
+        <v>146.0533447265625</v>
       </c>
       <c r="C224" t="n">
         <v>160.4700012207031</v>
@@ -6487,7 +6487,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>136.1652221679688</v>
+        <v>136.1652374267578</v>
       </c>
       <c r="C225" t="n">
         <v>147.9499969482422</v>
@@ -6516,7 +6516,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>135.5393829345703</v>
+        <v>135.5393981933594</v>
       </c>
       <c r="C226" t="n">
         <v>147.2700042724609</v>
@@ -6603,7 +6603,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>134.6627502441406</v>
+        <v>134.6627349853516</v>
       </c>
       <c r="C229" t="n">
         <v>144.8399963378906</v>
@@ -6632,7 +6632,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>138.7070922851562</v>
+        <v>138.7071075439453</v>
       </c>
       <c r="C230" t="n">
         <v>149.1900024414062</v>
@@ -6661,7 +6661,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>149.1102447509766</v>
+        <v>149.1102294921875</v>
       </c>
       <c r="C231" t="n">
         <v>158.6199951171875</v>
@@ -6690,7 +6690,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>157.2604370117188</v>
+        <v>157.2604522705078</v>
       </c>
       <c r="C232" t="n">
         <v>167.2899932861328</v>
@@ -6719,7 +6719,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>127.9027786254883</v>
+        <v>127.9027633666992</v>
       </c>
       <c r="C233" t="n">
         <v>136.0599975585938</v>
@@ -6748,7 +6748,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>130.0696411132812</v>
+        <v>130.0696258544922</v>
       </c>
       <c r="C234" t="n">
         <v>136.6999969482422</v>
@@ -6777,7 +6777,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>136.2448425292969</v>
+        <v>136.244873046875</v>
       </c>
       <c r="C235" t="n">
         <v>143.1900024414062</v>
@@ -6806,7 +6806,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>144.2850036621094</v>
+        <v>144.2849884033203</v>
       </c>
       <c r="C236" t="n">
         <v>151.6399993896484</v>
@@ -6835,7 +6835,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>154.5115203857422</v>
+        <v>154.5115051269531</v>
       </c>
       <c r="C237" t="n">
         <v>160.6000061035156</v>
@@ -6864,7 +6864,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>149.4028167724609</v>
+        <v>149.4028015136719</v>
       </c>
       <c r="C238" t="n">
         <v>155.2899932861328</v>
@@ -6893,7 +6893,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>151.7406921386719</v>
+        <v>151.7407073974609</v>
       </c>
       <c r="C239" t="n">
         <v>157.7200012207031</v>
@@ -6980,7 +6980,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>172.0943603515625</v>
+        <v>172.0943756103516</v>
       </c>
       <c r="C242" t="n">
         <v>176.8999938964844</v>
